--- a/academics/CABD/2025-2/CABD 2025-2.xlsx
+++ b/academics/CABD/2025-2/CABD 2025-2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\UAO\oicampo-uao.github.io\academics\CABD\2025-2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\oicampo\Documents\GitHub\oicampo-uao.github.io\academics\CABD\2025-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{109248CD-FB34-43C4-A27E-29E5B8C43D4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF57906C-CC64-4212-B90E-5284DF3E5827}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A6706BE5-6C63-4BDD-8165-A67704DFB86B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{A6706BE5-6C63-4BDD-8165-A67704DFB86B}"/>
   </bookViews>
   <sheets>
     <sheet name="CABD 2025-2" sheetId="1" r:id="rId1"/>
@@ -1920,18 +1920,6 @@
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="21" fontId="0" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -1951,51 +1939,63 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="19" fillId="34" borderId="0" xfId="42" applyFill="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="43">
-    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="Hyperlink" xfId="42" builtinId="8"/>
-    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="20% - Énfasis1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - Énfasis2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - Énfasis3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - Énfasis4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - Énfasis5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - Énfasis6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - Énfasis1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - Énfasis2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - Énfasis3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - Énfasis4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - Énfasis5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - Énfasis6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - Énfasis1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - Énfasis2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - Énfasis3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - Énfasis4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - Énfasis5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - Énfasis6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Bueno" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Cálculo" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Celda de comprobación" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Celda vinculada" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Encabezado 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Encabezado 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Énfasis1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Énfasis2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Énfasis3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Énfasis4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Énfasis5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Énfasis6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Entrada" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Hipervínculo" xfId="42" builtinId="8"/>
+    <cellStyle name="Incorrecto" xfId="7" builtinId="27" customBuiltin="1"/>
     <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Notas" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Salida" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Texto de advertencia" xfId="14" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="Texto explicativo" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Título" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Título 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Título 3" xfId="4" builtinId="18" customBuiltin="1"/>
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="57">
     <dxf>
@@ -2350,7 +2350,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -2667,7 +2667,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8DD2CE0-6169-477F-B8E1-2987D9E7C726}">
   <dimension ref="A1:BH37"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.42578125" customWidth="1"/>
     <col min="2" max="2" width="23.5703125" customWidth="1"/>
@@ -3095,20 +3095,20 @@
       </c>
       <c r="BH3" s="31"/>
     </row>
-    <row r="4" spans="1:60" s="60" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="60">
+    <row r="4" spans="1:60" s="56" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="56">
         <v>17</v>
       </c>
-      <c r="B4" s="60" t="s">
+      <c r="B4" s="56" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="60" t="s">
+      <c r="C4" s="56" t="s">
         <v>94</v>
       </c>
-      <c r="D4" s="60">
+      <c r="D4" s="56">
         <v>1110286885</v>
       </c>
-      <c r="E4" s="60" t="s">
+      <c r="E4" s="56" t="s">
         <v>28</v>
       </c>
       <c r="F4" s="9">
@@ -3139,81 +3139,81 @@
         <f t="shared" ref="M4:M34" si="3">IF(L4/$M$2&lt;=1.001,L4/$M$2,0.6)</f>
         <v>0.97352342158859484</v>
       </c>
-      <c r="N4" s="61">
+      <c r="N4" s="57">
         <v>4.5590277777777778E-2</v>
       </c>
       <c r="O4" s="10">
         <f t="shared" ref="O4:O34" si="4">IF(N4/$O$2&lt;=1.001,N4/$O$2,0.6)</f>
         <v>0.97717687918630614</v>
       </c>
-      <c r="P4" s="61">
+      <c r="P4" s="57">
         <v>4.3206018518518519E-2</v>
       </c>
       <c r="Q4" s="10">
         <f t="shared" ref="Q4:Q34" si="5">IF(P4/$Q$2&lt;=1.001,P4/$Q$2,0.6)</f>
         <v>1</v>
       </c>
-      <c r="R4" s="62">
+      <c r="R4" s="58">
         <f>AVERAGE(G4,I4,K4,M4,Table1[[#This Row],[%Conexión5]],Table1[[#This Row],[%Conexión6]])*5</f>
         <v>4.9437732220431609</v>
       </c>
-      <c r="S4" s="63">
+      <c r="S4" s="59">
         <v>1</v>
       </c>
-      <c r="T4" s="62" t="str" cm="1">
+      <c r="T4" s="58" t="str" cm="1">
         <f t="array" ref="T4">_xlfn.IFS(Table1[[#This Row],[Grupo]]=1,Sheet2!$B$1,Table1[[#This Row],[Grupo]]=2,Sheet2!$B$2,Table1[[#This Row],[Grupo]]=3,Sheet2!$B$3,Table1[[#This Row],[Grupo]]=4,Sheet2!$B$4,Table1[[#This Row],[Grupo]]=5,Sheet2!$B$5,Table1[[#This Row],[Grupo]]=6,Sheet2!$B$6,Table1[[#This Row],[Grupo]]=7,Sheet2!$B$7,Table1[[#This Row],[Grupo]]="","--")</f>
         <v>Gesto correspondiente a la palabra "Tortuga" en el lenguaje de señas colombiano</v>
       </c>
-      <c r="U4" s="64">
+      <c r="U4" s="60">
         <v>4</v>
       </c>
-      <c r="V4" s="64">
-        <v>0</v>
-      </c>
-      <c r="W4" s="64">
+      <c r="V4" s="60">
+        <v>0</v>
+      </c>
+      <c r="W4" s="60">
         <v>2.1</v>
       </c>
-      <c r="X4" s="64">
+      <c r="X4" s="60">
         <v>1.1000000000000001</v>
       </c>
-      <c r="Y4" s="64">
-        <v>0</v>
-      </c>
-      <c r="Z4" s="64">
+      <c r="Y4" s="60">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="60">
         <v>1.7</v>
       </c>
-      <c r="AA4" s="65">
+      <c r="AA4" s="61">
         <f>AVERAGE(Table1[[#This Row],[Operaciones sobre piezas (Semana 2) ]:[Escaneo de partes anatómicas (Semana 6) ]])*0.7+Table1[[#This Row],[Asistencia]]*0.3</f>
         <v>2.1691319666129485</v>
       </c>
-      <c r="AB4" s="61">
+      <c r="AB4" s="57">
         <v>4.1203703703703701E-2</v>
       </c>
       <c r="AC4" s="10">
         <f t="shared" ref="AC4:AC34" si="6">IF(AB4/$AC$2&lt;=1.01,AB4/$AC$2,0.6)</f>
         <v>1.0011248593925759</v>
       </c>
-      <c r="AD4" s="61">
+      <c r="AD4" s="57">
         <v>3.7314814814814815E-2</v>
       </c>
       <c r="AE4" s="10">
         <f t="shared" ref="AE4:AE34" si="7">IF(AD4/$AE$2&lt;=1.01,AD4/$AE$2,0.6)</f>
         <v>0.99414122725871112</v>
       </c>
-      <c r="AF4" s="61">
+      <c r="AF4" s="57">
         <v>3.8368055555555558E-2</v>
       </c>
       <c r="AG4" s="10">
         <v>1</v>
       </c>
-      <c r="AH4" s="61">
+      <c r="AH4" s="57">
         <v>1.4722222222222222E-2</v>
       </c>
       <c r="AI4" s="10">
         <f t="shared" ref="AI4:AI13" si="8">IF(AH4/$AI$2&lt;=1.01,AH4/$AI$2,0.6)</f>
         <v>1</v>
       </c>
-      <c r="AJ4" s="61">
+      <c r="AJ4" s="57">
         <v>2.6469907407407407E-2</v>
       </c>
       <c r="AK4" s="10">
@@ -3227,71 +3227,71 @@
         <f t="shared" ref="AM4:AM34" si="10">IF(AL4/$AM$2&lt;=1.01,AL4/$AM$2,0.6)</f>
         <v>0.40872250096487839</v>
       </c>
-      <c r="AN4" s="62">
+      <c r="AN4" s="58">
         <f t="shared" ref="AN4:AN34" si="11">AVERAGE(AC4,AE4,AG4,AI4,AK4,AM4)*5</f>
         <v>4.2839831872746394</v>
       </c>
-      <c r="AO4" s="65">
+      <c r="AO4" s="61">
         <v>5</v>
       </c>
-      <c r="AP4" s="65">
+      <c r="AP4" s="61">
         <v>2.5</v>
       </c>
-      <c r="AQ4" s="62">
+      <c r="AQ4" s="58">
         <f>Table1[[#This Row],[Asistencia 2o Corte]]*0.3+AVERAGE(Table1[[#This Row],[Tarea:Introducción a 3DSlicer (Semana 8) (Real)]:[Tarea:Segmentación Manual y Semi-Automática (Semana 10) (Real)]])*0.7</f>
         <v>3.9101949561823917</v>
       </c>
-      <c r="AR4" s="62"/>
-      <c r="AS4" s="62" t="s">
+      <c r="AR4" s="58"/>
+      <c r="AS4" s="58" t="s">
         <v>273</v>
       </c>
-      <c r="AT4" s="62" t="s">
+      <c r="AT4" s="58" t="s">
         <v>289</v>
       </c>
-      <c r="AU4" s="61">
+      <c r="AU4" s="57">
         <v>3.2835648148148149E-2</v>
       </c>
-      <c r="AV4" s="62">
+      <c r="AV4" s="58">
         <f t="shared" ref="AV4:AV34" si="12">IF(AU4/$AV$2&lt;=1.01,AU4/$AV$2,0.6)</f>
         <v>0.88435162094763087</v>
       </c>
-      <c r="AW4" s="61">
+      <c r="AW4" s="57">
         <v>3.2650462962962964E-2</v>
       </c>
-      <c r="AX4" s="62">
+      <c r="AX4" s="58">
         <f t="shared" ref="AX4:AX34" si="13">IF(AW4/$AX$2&lt;=1.01,AW4/$AX$2,0.6)</f>
         <v>1</v>
       </c>
-      <c r="AY4" s="61">
+      <c r="AY4" s="57">
         <v>3.6481481481481483E-2</v>
       </c>
-      <c r="AZ4" s="62">
+      <c r="AZ4" s="58">
         <f t="shared" ref="AZ4:AZ34" si="14">IF(AY4/$AZ$2&lt;=1.01,AY4/$AZ$2,0.6)</f>
         <v>1.0035020694046481</v>
       </c>
-      <c r="BA4" s="61">
+      <c r="BA4" s="57">
         <v>3.1365740740740743E-2</v>
       </c>
-      <c r="BB4" s="62">
+      <c r="BB4" s="58">
         <f t="shared" ref="BB4:BB34" si="15">IF(BA4/$BB$2&lt;=1.01,BA4/$BB$2,0.6)</f>
         <v>0.92082908596670066</v>
       </c>
-      <c r="BC4" s="62" t="s">
+      <c r="BC4" s="58" t="s">
         <v>312</v>
       </c>
-      <c r="BD4" s="62" t="s">
+      <c r="BD4" s="58" t="s">
         <v>319</v>
       </c>
-      <c r="BE4" s="66" t="s">
+      <c r="BE4" s="62" t="s">
         <v>326</v>
       </c>
-      <c r="BF4" s="62" t="s">
+      <c r="BF4" s="58" t="s">
         <v>339</v>
       </c>
-      <c r="BG4" s="66" t="s">
+      <c r="BG4" s="62" t="s">
         <v>340</v>
       </c>
-      <c r="BH4" s="62" t="s">
+      <c r="BH4" s="58" t="s">
         <v>348</v>
       </c>
     </row>
@@ -4241,20 +4241,20 @@
       </c>
       <c r="BG9" s="4"/>
     </row>
-    <row r="10" spans="1:60" s="60" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="60">
+    <row r="10" spans="1:60" s="56" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="56">
         <v>12</v>
       </c>
-      <c r="B10" s="60" t="s">
+      <c r="B10" s="56" t="s">
         <v>89</v>
       </c>
-      <c r="C10" s="60" t="s">
+      <c r="C10" s="56" t="s">
         <v>90</v>
       </c>
-      <c r="D10" s="60">
+      <c r="D10" s="56">
         <v>1107837413</v>
       </c>
-      <c r="E10" s="60" t="s">
+      <c r="E10" s="56" t="s">
         <v>57</v>
       </c>
       <c r="F10" s="9">
@@ -4285,82 +4285,82 @@
         <f t="shared" si="3"/>
         <v>0.90784114052953158</v>
       </c>
-      <c r="N10" s="61">
+      <c r="N10" s="57">
         <v>0</v>
       </c>
       <c r="O10" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="P10" s="61">
+      <c r="P10" s="57">
         <v>3.9016203703703706E-2</v>
       </c>
       <c r="Q10" s="10">
         <f t="shared" si="5"/>
         <v>0.90302705598714172</v>
       </c>
-      <c r="R10" s="62">
+      <c r="R10" s="58">
         <f>AVERAGE(G10,I10,K10,M10,Table1[[#This Row],[%Conexión5]],Table1[[#This Row],[%Conexión6]])*5</f>
         <v>3.1325140276311076</v>
       </c>
-      <c r="S10" s="63">
+      <c r="S10" s="59">
         <v>2</v>
       </c>
-      <c r="T10" s="62" t="str" cm="1">
+      <c r="T10" s="58" t="str" cm="1">
         <f t="array" ref="T10">_xlfn.IFS(Table1[[#This Row],[Grupo]]=1,Sheet2!$B$1,Table1[[#This Row],[Grupo]]=2,Sheet2!$B$2,Table1[[#This Row],[Grupo]]=3,Sheet2!$B$3,Table1[[#This Row],[Grupo]]=4,Sheet2!$B$4,Table1[[#This Row],[Grupo]]=5,Sheet2!$B$5,Table1[[#This Row],[Grupo]]=6,Sheet2!$B$6,Table1[[#This Row],[Grupo]]=7,Sheet2!$B$7,Table1[[#This Row],[Grupo]]="","--")</f>
         <v>Gesto correspondiente a la palabra "Ratón" en el lenguaje de señas colombiano</v>
       </c>
-      <c r="U10" s="64">
-        <v>0</v>
-      </c>
-      <c r="V10" s="64">
+      <c r="U10" s="60">
+        <v>0</v>
+      </c>
+      <c r="V10" s="60">
         <v>3.9</v>
       </c>
-      <c r="W10" s="64">
+      <c r="W10" s="60">
         <v>5</v>
       </c>
-      <c r="X10" s="64">
+      <c r="X10" s="60">
         <v>3.3</v>
       </c>
-      <c r="Y10" s="64">
+      <c r="Y10" s="60">
         <v>5</v>
       </c>
-      <c r="Z10" s="64">
+      <c r="Z10" s="60">
         <v>4.5</v>
       </c>
-      <c r="AA10" s="65">
+      <c r="AA10" s="61">
         <f>AVERAGE(Table1[[#This Row],[Operaciones sobre piezas (Semana 2) ]:[Escaneo de partes anatómicas (Semana 6) ]])*0.7+Table1[[#This Row],[Asistencia]]*0.3</f>
         <v>3.977754208289332</v>
       </c>
-      <c r="AB10" s="61">
+      <c r="AB10" s="57">
         <v>3.8090277777777778E-2</v>
       </c>
       <c r="AC10" s="10">
         <f t="shared" si="6"/>
         <v>0.92547806524184484</v>
       </c>
-      <c r="AD10" s="61">
+      <c r="AD10" s="57">
         <v>3.7384259259259256E-2</v>
       </c>
       <c r="AE10" s="10">
         <f t="shared" si="7"/>
         <v>0.99599136601911809</v>
       </c>
-      <c r="AF10" s="61">
+      <c r="AF10" s="57">
         <v>2.8125000000000001E-2</v>
       </c>
       <c r="AG10" s="10">
         <f>IF(AF10/$AG$2&lt;=1.01,AF10/$AG$2,0.6)</f>
         <v>0.74930619796484743</v>
       </c>
-      <c r="AH10" s="61">
+      <c r="AH10" s="57">
         <v>1.4722222222222222E-2</v>
       </c>
       <c r="AI10" s="10">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="AJ10" s="61">
+      <c r="AJ10" s="57">
         <v>0</v>
       </c>
       <c r="AK10" s="10">
@@ -4374,61 +4374,61 @@
         <f t="shared" si="10"/>
         <v>0.99845619451949053</v>
       </c>
-      <c r="AN10" s="62">
+      <c r="AN10" s="58">
         <f t="shared" si="11"/>
         <v>3.8910265197877507</v>
       </c>
-      <c r="AO10" s="65">
+      <c r="AO10" s="61">
         <v>5</v>
       </c>
-      <c r="AP10" s="65">
-        <v>0</v>
-      </c>
-      <c r="AQ10" s="62">
+      <c r="AP10" s="61">
+        <v>0</v>
+      </c>
+      <c r="AQ10" s="58">
         <f>Table1[[#This Row],[Asistencia 2o Corte]]*0.3+AVERAGE(Table1[[#This Row],[Tarea:Introducción a 3DSlicer (Semana 8) (Real)]:[Tarea:Segmentación Manual y Semi-Automática (Semana 10) (Real)]])*0.7</f>
         <v>2.9173079559363249</v>
       </c>
-      <c r="AR10" s="62"/>
-      <c r="AS10" s="62"/>
-      <c r="AT10" s="62"/>
-      <c r="AU10" s="61">
+      <c r="AR10" s="58"/>
+      <c r="AS10" s="58"/>
+      <c r="AT10" s="58"/>
+      <c r="AU10" s="57">
         <v>2.9537037037037039E-2</v>
       </c>
-      <c r="AV10" s="62">
+      <c r="AV10" s="58">
         <f t="shared" si="12"/>
         <v>0.79551122194513724</v>
       </c>
-      <c r="AW10" s="61">
+      <c r="AW10" s="57">
         <v>3.2650462962962964E-2</v>
       </c>
-      <c r="AX10" s="62">
+      <c r="AX10" s="58">
         <f t="shared" si="13"/>
         <v>1</v>
       </c>
-      <c r="AY10" s="61">
+      <c r="AY10" s="57">
         <v>1.5347222222222222E-2</v>
       </c>
-      <c r="AZ10" s="62">
+      <c r="AZ10" s="58">
         <f t="shared" si="14"/>
         <v>0.42215854823304683</v>
       </c>
-      <c r="BA10" s="61">
-        <v>0</v>
-      </c>
-      <c r="BB10" s="62">
+      <c r="BA10" s="57">
+        <v>0</v>
+      </c>
+      <c r="BB10" s="58">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BC10" s="62"/>
-      <c r="BD10" s="62"/>
-      <c r="BE10" s="62"/>
-      <c r="BF10" s="62" t="s">
+      <c r="BC10" s="58"/>
+      <c r="BD10" s="58"/>
+      <c r="BE10" s="58"/>
+      <c r="BF10" s="58" t="s">
         <v>345</v>
       </c>
-      <c r="BG10" s="62" t="s">
+      <c r="BG10" s="58" t="s">
         <v>339</v>
       </c>
-      <c r="BH10" s="62" t="s">
+      <c r="BH10" s="58" t="s">
         <v>354</v>
       </c>
     </row>
@@ -5002,20 +5002,20 @@
       </c>
       <c r="BG13" s="4"/>
     </row>
-    <row r="14" spans="1:60" s="60" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="60">
+    <row r="14" spans="1:60" s="56" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="56">
         <v>30</v>
       </c>
-      <c r="B14" s="67" t="s">
+      <c r="B14" s="63" t="s">
         <v>56</v>
       </c>
-      <c r="C14" s="67" t="s">
+      <c r="C14" s="63" t="s">
         <v>107</v>
       </c>
-      <c r="D14" s="60">
+      <c r="D14" s="56">
         <v>73265790</v>
       </c>
-      <c r="E14" s="68" t="s">
+      <c r="E14" s="64" t="s">
         <v>60</v>
       </c>
       <c r="F14" s="9">
@@ -5046,80 +5046,80 @@
         <f t="shared" si="3"/>
         <v>0.93431771894093685</v>
       </c>
-      <c r="N14" s="61">
+      <c r="N14" s="57">
         <v>4.659722222222222E-2</v>
       </c>
       <c r="O14" s="10">
         <f t="shared" si="4"/>
         <v>0.99875961299925564</v>
       </c>
-      <c r="P14" s="61">
+      <c r="P14" s="57">
         <v>4.1886574074074076E-2</v>
       </c>
       <c r="Q14" s="10">
         <f t="shared" si="5"/>
         <v>0.96946155906777398</v>
       </c>
-      <c r="R14" s="62">
+      <c r="R14" s="58">
         <f>AVERAGE(G14,I14,K14,M14,Table1[[#This Row],[%Conexión5]],Table1[[#This Row],[%Conexión6]])*5</f>
         <v>4.5809297742207793</v>
       </c>
-      <c r="S14" s="63">
+      <c r="S14" s="59">
         <v>3</v>
       </c>
-      <c r="T14" s="62" t="str" cm="1">
+      <c r="T14" s="58" t="str" cm="1">
         <f t="array" ref="T14">_xlfn.IFS(Table1[[#This Row],[Grupo]]=1,Sheet2!$B$1,Table1[[#This Row],[Grupo]]=2,Sheet2!$B$2,Table1[[#This Row],[Grupo]]=3,Sheet2!$B$3,Table1[[#This Row],[Grupo]]=4,Sheet2!$B$4,Table1[[#This Row],[Grupo]]=5,Sheet2!$B$5,Table1[[#This Row],[Grupo]]=6,Sheet2!$B$6,Table1[[#This Row],[Grupo]]=7,Sheet2!$B$7,Table1[[#This Row],[Grupo]]="","--")</f>
         <v>Gesto correspondiente a la palabra "Oveja" en el lenguaje de señas colombiano</v>
       </c>
-      <c r="U14" s="64">
+      <c r="U14" s="60">
         <v>4.9000000000000004</v>
       </c>
-      <c r="V14" s="64">
+      <c r="V14" s="60">
         <v>3.9</v>
       </c>
-      <c r="W14" s="64">
+      <c r="W14" s="60">
         <v>4.5</v>
       </c>
-      <c r="X14" s="64">
+      <c r="X14" s="60">
         <v>5</v>
       </c>
-      <c r="Y14" s="64">
+      <c r="Y14" s="60">
         <v>5</v>
       </c>
-      <c r="Z14" s="64">
+      <c r="Z14" s="60">
         <v>4.5</v>
       </c>
-      <c r="AA14" s="65">
+      <c r="AA14" s="61">
         <f>AVERAGE(Table1[[#This Row],[Operaciones sobre piezas (Semana 2) ]:[Escaneo de partes anatómicas (Semana 6) ]])*0.7+Table1[[#This Row],[Asistencia]]*0.3</f>
         <v>4.5802789322662338</v>
       </c>
-      <c r="AB14" s="61">
+      <c r="AB14" s="57">
         <v>3.8425925925925926E-2</v>
       </c>
       <c r="AC14" s="10">
         <f t="shared" si="6"/>
         <v>0.93363329583802024</v>
       </c>
-      <c r="AD14" s="61">
+      <c r="AD14" s="57">
         <v>3.7256944444444447E-2</v>
       </c>
       <c r="AE14" s="10">
         <f t="shared" si="7"/>
         <v>0.99259944495837205</v>
       </c>
-      <c r="AF14" s="61">
+      <c r="AF14" s="57">
         <v>3.8368055555555558E-2</v>
       </c>
       <c r="AG14" s="10">
         <v>1</v>
       </c>
-      <c r="AH14" s="61">
+      <c r="AH14" s="57">
         <v>2.855324074074074E-2</v>
       </c>
       <c r="AI14" s="10">
         <v>1</v>
       </c>
-      <c r="AJ14" s="61">
+      <c r="AJ14" s="57">
         <v>1.4675925925925926E-2</v>
       </c>
       <c r="AK14" s="10">
@@ -5133,78 +5133,78 @@
         <f t="shared" si="10"/>
         <v>0.34890003859513702</v>
       </c>
-      <c r="AN14" s="62">
+      <c r="AN14" s="58">
         <f t="shared" si="11"/>
         <v>3.9030316116922541</v>
       </c>
-      <c r="AO14" s="65">
+      <c r="AO14" s="61">
         <v>4.4000000000000004</v>
       </c>
-      <c r="AP14" s="65">
+      <c r="AP14" s="61">
         <v>3.8</v>
       </c>
-      <c r="AQ14" s="62">
+      <c r="AQ14" s="58">
         <f>Table1[[#This Row],[Asistencia 2o Corte]]*0.3+AVERAGE(Table1[[#This Row],[Tarea:Introducción a 3DSlicer (Semana 8) (Real)]:[Tarea:Segmentación Manual y Semi-Automática (Semana 10) (Real)]])*0.7</f>
         <v>4.0409094835076758</v>
       </c>
-      <c r="AR14" s="62"/>
-      <c r="AS14" s="62"/>
-      <c r="AT14" s="62"/>
-      <c r="AU14" s="61">
-        <v>0</v>
-      </c>
-      <c r="AV14" s="62">
+      <c r="AR14" s="58"/>
+      <c r="AS14" s="58"/>
+      <c r="AT14" s="58"/>
+      <c r="AU14" s="57">
+        <v>0</v>
+      </c>
+      <c r="AV14" s="58">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AW14" s="61">
+      <c r="AW14" s="57">
         <v>3.2650462962962964E-2</v>
       </c>
-      <c r="AX14" s="62">
+      <c r="AX14" s="58">
         <f t="shared" si="13"/>
         <v>1</v>
       </c>
-      <c r="AY14" s="61">
-        <v>0</v>
-      </c>
-      <c r="AZ14" s="62">
+      <c r="AY14" s="57">
+        <v>0</v>
+      </c>
+      <c r="AZ14" s="58">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BA14" s="61">
+      <c r="BA14" s="57">
         <v>1.9444444444444444E-3</v>
       </c>
-      <c r="BB14" s="62">
+      <c r="BB14" s="58">
         <f t="shared" si="15"/>
         <v>5.7084607543323132E-2</v>
       </c>
-      <c r="BC14" s="62"/>
-      <c r="BD14" s="62"/>
-      <c r="BE14" s="62"/>
-      <c r="BF14" s="62" t="s">
+      <c r="BC14" s="58"/>
+      <c r="BD14" s="58"/>
+      <c r="BE14" s="58"/>
+      <c r="BF14" s="58" t="s">
         <v>339</v>
       </c>
-      <c r="BG14" s="66" t="s">
+      <c r="BG14" s="62" t="s">
         <v>345</v>
       </c>
-      <c r="BH14" s="62" t="s">
+      <c r="BH14" s="58" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="15" spans="1:60" s="60" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="60">
+    <row r="15" spans="1:60" s="56" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="56">
         <v>11</v>
       </c>
-      <c r="B15" s="60" t="s">
+      <c r="B15" s="56" t="s">
         <v>31</v>
       </c>
-      <c r="C15" s="60" t="s">
+      <c r="C15" s="56" t="s">
         <v>88</v>
       </c>
-      <c r="D15" s="60">
+      <c r="D15" s="56">
         <v>1110285503</v>
       </c>
-      <c r="E15" s="60" t="s">
+      <c r="E15" s="56" t="s">
         <v>32</v>
       </c>
       <c r="F15" s="9">
@@ -5235,81 +5235,81 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N15" s="61">
+      <c r="N15" s="57">
         <v>4.327546296296296E-2</v>
       </c>
       <c r="O15" s="10">
         <f t="shared" si="4"/>
         <v>0.92756139915653668</v>
       </c>
-      <c r="P15" s="61">
+      <c r="P15" s="57">
         <v>4.3182870370370371E-2</v>
       </c>
       <c r="Q15" s="10">
         <f t="shared" si="5"/>
         <v>0.99946423787838201</v>
       </c>
-      <c r="R15" s="62">
+      <c r="R15" s="58">
         <f>AVERAGE(G15,I15,K15,M15,Table1[[#This Row],[%Conexión5]],Table1[[#This Row],[%Conexión6]])*5</f>
         <v>3.2540732041625784</v>
       </c>
-      <c r="S15" s="63">
+      <c r="S15" s="59">
         <v>4</v>
       </c>
-      <c r="T15" s="62" t="str" cm="1">
+      <c r="T15" s="58" t="str" cm="1">
         <f t="array" ref="T15">_xlfn.IFS(Table1[[#This Row],[Grupo]]=1,Sheet2!$B$1,Table1[[#This Row],[Grupo]]=2,Sheet2!$B$2,Table1[[#This Row],[Grupo]]=3,Sheet2!$B$3,Table1[[#This Row],[Grupo]]=4,Sheet2!$B$4,Table1[[#This Row],[Grupo]]=5,Sheet2!$B$5,Table1[[#This Row],[Grupo]]=6,Sheet2!$B$6,Table1[[#This Row],[Grupo]]=7,Sheet2!$B$7,Table1[[#This Row],[Grupo]]="","--")</f>
         <v>Gesto correspondiente a la palabra "Durazno" en el lenguaje de señas colombiano</v>
       </c>
-      <c r="U15" s="64">
+      <c r="U15" s="60">
         <v>5</v>
       </c>
-      <c r="V15" s="64">
+      <c r="V15" s="60">
         <v>4</v>
       </c>
-      <c r="W15" s="64">
+      <c r="W15" s="60">
         <v>0.6</v>
       </c>
-      <c r="X15" s="64">
+      <c r="X15" s="60">
         <v>5</v>
       </c>
-      <c r="Y15" s="64">
+      <c r="Y15" s="60">
         <v>5</v>
       </c>
-      <c r="Z15" s="64">
+      <c r="Z15" s="60">
         <v>4.5</v>
       </c>
-      <c r="AA15" s="65">
+      <c r="AA15" s="61">
         <f>AVERAGE(Table1[[#This Row],[Operaciones sobre piezas (Semana 2) ]:[Escaneo de partes anatómicas (Semana 6) ]])*0.7+Table1[[#This Row],[Asistencia]]*0.3</f>
         <v>3.6502219612487732</v>
       </c>
-      <c r="AB15" s="61">
+      <c r="AB15" s="57">
         <v>3.7256944444444447E-2</v>
       </c>
       <c r="AC15" s="10">
         <f t="shared" si="6"/>
         <v>0.90523059617547819</v>
       </c>
-      <c r="AD15" s="61">
+      <c r="AD15" s="57">
         <v>0</v>
       </c>
       <c r="AE15" s="10">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AF15" s="61">
+      <c r="AF15" s="57">
         <v>3.8368055555555558E-2</v>
       </c>
       <c r="AG15" s="10">
         <v>1</v>
       </c>
-      <c r="AH15" s="61">
+      <c r="AH15" s="57">
         <v>1.412037037037037E-2</v>
       </c>
       <c r="AI15" s="10">
         <f t="shared" ref="AI15:AI34" si="16">IF(AH15/$AI$2&lt;=1.01,AH15/$AI$2,0.6)</f>
         <v>0.95911949685534592</v>
       </c>
-      <c r="AJ15" s="61">
+      <c r="AJ15" s="57">
         <v>2.2407407407407407E-2</v>
       </c>
       <c r="AK15" s="10">
@@ -5323,71 +5323,71 @@
         <f t="shared" si="10"/>
         <v>0.92937089926669236</v>
       </c>
-      <c r="AN15" s="62">
+      <c r="AN15" s="58">
         <f t="shared" si="11"/>
         <v>3.6811936104197525</v>
       </c>
-      <c r="AO15" s="65">
+      <c r="AO15" s="61">
         <v>5</v>
       </c>
-      <c r="AP15" s="65">
+      <c r="AP15" s="61">
         <v>3.6</v>
       </c>
-      <c r="AQ15" s="62">
+      <c r="AQ15" s="58">
         <f>Table1[[#This Row],[Asistencia 2o Corte]]*0.3+AVERAGE(Table1[[#This Row],[Tarea:Introducción a 3DSlicer (Semana 8) (Real)]:[Tarea:Segmentación Manual y Semi-Automática (Semana 10) (Real)]])*0.7</f>
         <v>4.114358083125925</v>
       </c>
-      <c r="AR15" s="62"/>
-      <c r="AS15" s="62" t="s">
+      <c r="AR15" s="58"/>
+      <c r="AS15" s="58" t="s">
         <v>275</v>
       </c>
-      <c r="AT15" s="62" t="s">
+      <c r="AT15" s="58" t="s">
         <v>293</v>
       </c>
-      <c r="AU15" s="61">
-        <v>0</v>
-      </c>
-      <c r="AV15" s="62">
+      <c r="AU15" s="57">
+        <v>0</v>
+      </c>
+      <c r="AV15" s="58">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AW15" s="61">
+      <c r="AW15" s="57">
         <v>3.2650462962962964E-2</v>
       </c>
-      <c r="AX15" s="62">
+      <c r="AX15" s="58">
         <f t="shared" si="13"/>
         <v>1</v>
       </c>
-      <c r="AY15" s="61">
+      <c r="AY15" s="57">
         <v>2.2511574074074073E-2</v>
       </c>
-      <c r="AZ15" s="62">
+      <c r="AZ15" s="58">
         <f t="shared" si="14"/>
         <v>0.61922954473097735</v>
       </c>
-      <c r="BA15" s="61">
-        <v>0</v>
-      </c>
-      <c r="BB15" s="62">
+      <c r="BA15" s="57">
+        <v>0</v>
+      </c>
+      <c r="BB15" s="58">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BC15" s="62" t="s">
+      <c r="BC15" s="58" t="s">
         <v>313</v>
       </c>
-      <c r="BD15" s="62" t="s">
+      <c r="BD15" s="58" t="s">
         <v>324</v>
       </c>
-      <c r="BE15" s="66" t="s">
+      <c r="BE15" s="62" t="s">
         <v>329</v>
       </c>
-      <c r="BF15" s="62" t="s">
+      <c r="BF15" s="58" t="s">
         <v>340</v>
       </c>
-      <c r="BG15" s="62" t="s">
+      <c r="BG15" s="58" t="s">
         <v>339</v>
       </c>
-      <c r="BH15" s="62" t="s">
+      <c r="BH15" s="58" t="s">
         <v>350</v>
       </c>
     </row>
@@ -6336,20 +6336,20 @@
       <c r="BG20" s="4"/>
       <c r="BH20" s="4"/>
     </row>
-    <row r="21" spans="1:60" s="60" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="60">
+    <row r="21" spans="1:60" s="56" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="56">
         <v>24</v>
       </c>
-      <c r="B21" s="60" t="s">
+      <c r="B21" s="56" t="s">
         <v>17</v>
       </c>
-      <c r="C21" s="60" t="s">
+      <c r="C21" s="56" t="s">
         <v>102</v>
       </c>
-      <c r="D21" s="60">
+      <c r="D21" s="56">
         <v>1112041894</v>
       </c>
-      <c r="E21" s="60" t="s">
+      <c r="E21" s="56" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="9">
@@ -6380,82 +6380,82 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N21" s="61">
+      <c r="N21" s="57">
         <v>4.1226851851851855E-2</v>
       </c>
       <c r="O21" s="10">
         <f t="shared" si="4"/>
         <v>0.88365169933019105</v>
       </c>
-      <c r="P21" s="61">
+      <c r="P21" s="57">
         <v>4.2858796296296298E-2</v>
       </c>
       <c r="Q21" s="10">
         <f t="shared" si="5"/>
         <v>0.99196356817573006</v>
       </c>
-      <c r="R21" s="62">
+      <c r="R21" s="58">
         <f>AVERAGE(G21,I21,K21,M21,Table1[[#This Row],[%Conexión5]],Table1[[#This Row],[%Conexión6]])*5</f>
         <v>2.6320651911594055</v>
       </c>
-      <c r="S21" s="63">
+      <c r="S21" s="59">
         <v>5</v>
       </c>
-      <c r="T21" s="62" t="str" cm="1">
+      <c r="T21" s="58" t="str" cm="1">
         <f t="array" ref="T21">_xlfn.IFS(Table1[[#This Row],[Grupo]]=1,Sheet2!$B$1,Table1[[#This Row],[Grupo]]=2,Sheet2!$B$2,Table1[[#This Row],[Grupo]]=3,Sheet2!$B$3,Table1[[#This Row],[Grupo]]=4,Sheet2!$B$4,Table1[[#This Row],[Grupo]]=5,Sheet2!$B$5,Table1[[#This Row],[Grupo]]=6,Sheet2!$B$6,Table1[[#This Row],[Grupo]]=7,Sheet2!$B$7,Table1[[#This Row],[Grupo]]="","--")</f>
         <v>Gesto correspondiente a la palabra "Caracol" en el lenguaje de señas colombiano</v>
       </c>
-      <c r="U21" s="64">
+      <c r="U21" s="60">
         <v>1</v>
       </c>
-      <c r="V21" s="64">
+      <c r="V21" s="60">
         <v>2.5</v>
       </c>
-      <c r="W21" s="64">
+      <c r="W21" s="60">
         <v>2.8</v>
       </c>
-      <c r="X21" s="64">
+      <c r="X21" s="60">
         <v>3.3</v>
       </c>
-      <c r="Y21" s="64">
-        <v>0</v>
-      </c>
-      <c r="Z21" s="64">
+      <c r="Y21" s="60">
+        <v>0</v>
+      </c>
+      <c r="Z21" s="60">
         <v>4.5</v>
       </c>
-      <c r="AA21" s="65">
+      <c r="AA21" s="61">
         <f>AVERAGE(Table1[[#This Row],[Operaciones sobre piezas (Semana 2) ]:[Escaneo de partes anatómicas (Semana 6) ]])*0.7+Table1[[#This Row],[Asistencia]]*0.3</f>
         <v>2.6236195573478214</v>
       </c>
-      <c r="AB21" s="61">
+      <c r="AB21" s="57">
         <v>4.0208333333333332E-2</v>
       </c>
       <c r="AC21" s="10">
         <f t="shared" si="6"/>
         <v>0.9769403824521935</v>
       </c>
-      <c r="AD21" s="61">
+      <c r="AD21" s="57">
         <v>3.6712962962962961E-2</v>
       </c>
       <c r="AE21" s="10">
         <f t="shared" si="7"/>
         <v>0.97810669133518346</v>
       </c>
-      <c r="AF21" s="61">
+      <c r="AF21" s="57">
         <v>3.7557870370370373E-2</v>
       </c>
       <c r="AG21" s="10">
         <f>IF(AF21/$AG$2&lt;=1.01,AF21/$AG$2,0.6)</f>
         <v>1.0006167129201358</v>
       </c>
-      <c r="AH21" s="61">
+      <c r="AH21" s="57">
         <v>1.4722222222222222E-2</v>
       </c>
       <c r="AI21" s="10">
         <f t="shared" si="16"/>
         <v>1</v>
       </c>
-      <c r="AJ21" s="61">
+      <c r="AJ21" s="57">
         <v>3.4872685185185187E-2</v>
       </c>
       <c r="AK21" s="10">
@@ -6469,65 +6469,65 @@
         <f t="shared" si="10"/>
         <v>0.34890003859513702</v>
       </c>
-      <c r="AN21" s="62">
+      <c r="AN21" s="58">
         <f t="shared" si="11"/>
         <v>4.3960390124944766</v>
       </c>
-      <c r="AO21" s="65">
+      <c r="AO21" s="61">
         <v>5</v>
       </c>
-      <c r="AP21" s="65">
-        <v>0</v>
-      </c>
-      <c r="AQ21" s="62">
+      <c r="AP21" s="61">
+        <v>0</v>
+      </c>
+      <c r="AQ21" s="58">
         <f>Table1[[#This Row],[Asistencia 2o Corte]]*0.3+AVERAGE(Table1[[#This Row],[Tarea:Introducción a 3DSlicer (Semana 8) (Real)]:[Tarea:Segmentación Manual y Semi-Automática (Semana 10) (Real)]])*0.7</f>
         <v>3.0688117037483429</v>
       </c>
-      <c r="AR21" s="62"/>
-      <c r="AS21" s="62"/>
-      <c r="AT21" s="62" t="s">
+      <c r="AR21" s="58"/>
+      <c r="AS21" s="58"/>
+      <c r="AT21" s="58" t="s">
         <v>295</v>
       </c>
-      <c r="AU21" s="61">
+      <c r="AU21" s="57">
         <v>3.712962962962963E-2</v>
       </c>
-      <c r="AV21" s="62">
+      <c r="AV21" s="58">
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="AW21" s="61">
+      <c r="AW21" s="57">
         <v>2.255787037037037E-2</v>
       </c>
-      <c r="AX21" s="62">
+      <c r="AX21" s="58">
         <f t="shared" si="13"/>
         <v>0.69088975540588438</v>
       </c>
-      <c r="AY21" s="61">
-        <v>0</v>
-      </c>
-      <c r="AZ21" s="62">
+      <c r="AY21" s="57">
+        <v>0</v>
+      </c>
+      <c r="AZ21" s="58">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BA21" s="61">
+      <c r="BA21" s="57">
         <v>3.4074074074074076E-2</v>
       </c>
-      <c r="BB21" s="62">
+      <c r="BB21" s="58">
         <f t="shared" si="15"/>
         <v>1.000339789330615</v>
       </c>
-      <c r="BC21" s="62"/>
-      <c r="BD21" s="62" t="s">
+      <c r="BC21" s="58"/>
+      <c r="BD21" s="58" t="s">
         <v>321</v>
       </c>
-      <c r="BE21" s="62"/>
-      <c r="BF21" s="62" t="s">
+      <c r="BE21" s="58"/>
+      <c r="BF21" s="58" t="s">
         <v>346</v>
       </c>
-      <c r="BG21" s="66" t="s">
+      <c r="BG21" s="62" t="s">
         <v>340</v>
       </c>
-      <c r="BH21" s="66" t="s">
+      <c r="BH21" s="62" t="s">
         <v>351</v>
       </c>
     </row>
@@ -7102,20 +7102,20 @@
       <c r="BG24" s="4"/>
       <c r="BH24" s="4"/>
     </row>
-    <row r="25" spans="1:60" s="60" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="60">
+    <row r="25" spans="1:60" s="56" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="56">
         <v>28</v>
       </c>
-      <c r="B25" s="60" t="s">
+      <c r="B25" s="56" t="s">
         <v>52</v>
       </c>
-      <c r="C25" s="60" t="s">
+      <c r="C25" s="56" t="s">
         <v>105</v>
       </c>
-      <c r="D25" s="60">
+      <c r="D25" s="56">
         <v>1112389849</v>
       </c>
-      <c r="E25" s="60" t="s">
+      <c r="E25" s="56" t="s">
         <v>53</v>
       </c>
       <c r="F25" s="9">
@@ -7146,82 +7146,82 @@
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="N25" s="61">
+      <c r="N25" s="57">
         <v>4.659722222222222E-2</v>
       </c>
       <c r="O25" s="10">
         <f t="shared" si="4"/>
         <v>0.99875961299925564</v>
       </c>
-      <c r="P25" s="61">
+      <c r="P25" s="57">
         <v>4.189814814814815E-2</v>
       </c>
       <c r="Q25" s="10">
         <f t="shared" si="5"/>
         <v>0.96972944012858298</v>
       </c>
-      <c r="R25" s="62">
+      <c r="R25" s="58">
         <f>AVERAGE(G25,I25,K25,M25,Table1[[#This Row],[%Conexión5]],Table1[[#This Row],[%Conexión6]])*5</f>
         <v>4.6282070535838633</v>
       </c>
-      <c r="S25" s="63">
+      <c r="S25" s="59">
         <v>6</v>
       </c>
-      <c r="T25" s="62" t="str" cm="1">
+      <c r="T25" s="58" t="str" cm="1">
         <f t="array" ref="T25">_xlfn.IFS(Table1[[#This Row],[Grupo]]=1,Sheet2!$B$1,Table1[[#This Row],[Grupo]]=2,Sheet2!$B$2,Table1[[#This Row],[Grupo]]=3,Sheet2!$B$3,Table1[[#This Row],[Grupo]]=4,Sheet2!$B$4,Table1[[#This Row],[Grupo]]=5,Sheet2!$B$5,Table1[[#This Row],[Grupo]]=6,Sheet2!$B$6,Table1[[#This Row],[Grupo]]=7,Sheet2!$B$7,Table1[[#This Row],[Grupo]]="","--")</f>
         <v>Gesto correspondiente a la palabra "Caballo" en el lenguaje de señas colombiano</v>
       </c>
-      <c r="U25" s="64">
+      <c r="U25" s="60">
         <v>5</v>
       </c>
-      <c r="V25" s="64">
+      <c r="V25" s="60">
         <v>4.5999999999999996</v>
       </c>
-      <c r="W25" s="64">
+      <c r="W25" s="60">
         <v>4.8</v>
       </c>
-      <c r="X25" s="64">
+      <c r="X25" s="60">
         <v>3.3</v>
       </c>
-      <c r="Y25" s="64">
+      <c r="Y25" s="60">
         <v>5</v>
       </c>
-      <c r="Z25" s="64">
+      <c r="Z25" s="60">
         <v>3.5</v>
       </c>
-      <c r="AA25" s="65">
+      <c r="AA25" s="61">
         <f>AVERAGE(Table1[[#This Row],[Operaciones sobre piezas (Semana 2) ]:[Escaneo de partes anatómicas (Semana 6) ]])*0.7+Table1[[#This Row],[Asistencia]]*0.3</f>
         <v>4.3564621160751589</v>
       </c>
-      <c r="AB25" s="61">
+      <c r="AB25" s="57">
         <v>3.7615740740740741E-2</v>
       </c>
       <c r="AC25" s="10">
         <f t="shared" si="6"/>
         <v>0.91394825646794153</v>
       </c>
-      <c r="AD25" s="61">
+      <c r="AD25" s="57">
         <v>3.5624999999999997E-2</v>
       </c>
       <c r="AE25" s="10">
         <f t="shared" si="7"/>
         <v>0.94912118408880664</v>
       </c>
-      <c r="AF25" s="61">
+      <c r="AF25" s="57">
         <v>3.6076388888888887E-2</v>
       </c>
       <c r="AG25" s="10">
         <f>IF(AF25/$AG$2&lt;=1.01,AF25/$AG$2,0.6)</f>
         <v>0.96114708603145238</v>
       </c>
-      <c r="AH25" s="61">
+      <c r="AH25" s="57">
         <v>1.4722222222222222E-2</v>
       </c>
       <c r="AI25" s="10">
         <f t="shared" si="16"/>
         <v>1</v>
       </c>
-      <c r="AJ25" s="61">
+      <c r="AJ25" s="57">
         <v>3.1932870370370368E-2</v>
       </c>
       <c r="AK25" s="10">
@@ -7235,63 +7235,63 @@
         <f t="shared" si="10"/>
         <v>0.34890003859513702</v>
       </c>
-      <c r="AN25" s="62">
+      <c r="AN25" s="58">
         <f t="shared" si="11"/>
         <v>4.2183080483057029</v>
       </c>
-      <c r="AO25" s="65">
-        <v>0</v>
-      </c>
-      <c r="AP25" s="65">
+      <c r="AO25" s="61">
+        <v>0</v>
+      </c>
+      <c r="AP25" s="61">
         <v>3.4</v>
       </c>
-      <c r="AQ25" s="62">
+      <c r="AQ25" s="58">
         <f>Table1[[#This Row],[Asistencia 2o Corte]]*0.3+AVERAGE(Table1[[#This Row],[Tarea:Introducción a 3DSlicer (Semana 8) (Real)]:[Tarea:Segmentación Manual y Semi-Automática (Semana 10) (Real)]])*0.7</f>
         <v>2.4554924144917107</v>
       </c>
-      <c r="AR25" s="62"/>
-      <c r="AS25" s="62"/>
-      <c r="AT25" s="62"/>
-      <c r="AU25" s="61">
+      <c r="AR25" s="58"/>
+      <c r="AS25" s="58"/>
+      <c r="AT25" s="58"/>
+      <c r="AU25" s="57">
         <v>3.712962962962963E-2</v>
       </c>
-      <c r="AV25" s="62">
+      <c r="AV25" s="58">
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="AW25" s="61">
+      <c r="AW25" s="57">
         <v>3.2581018518518516E-2</v>
       </c>
-      <c r="AX25" s="62">
+      <c r="AX25" s="58">
         <f t="shared" si="13"/>
         <v>0.99787309464728813</v>
       </c>
-      <c r="AY25" s="61">
+      <c r="AY25" s="57">
         <v>3.2048611111111111E-2</v>
       </c>
-      <c r="AZ25" s="62">
+      <c r="AZ25" s="58">
         <f t="shared" si="14"/>
         <v>0.88156638013371535</v>
       </c>
-      <c r="BA25" s="61">
+      <c r="BA25" s="57">
         <v>3.4074074074074076E-2</v>
       </c>
-      <c r="BB25" s="62">
+      <c r="BB25" s="58">
         <f t="shared" si="15"/>
         <v>1.000339789330615</v>
       </c>
-      <c r="BC25" s="62"/>
-      <c r="BD25" s="62" t="s">
+      <c r="BC25" s="58"/>
+      <c r="BD25" s="58" t="s">
         <v>322</v>
       </c>
-      <c r="BE25" s="62"/>
-      <c r="BF25" s="62" t="s">
+      <c r="BE25" s="58"/>
+      <c r="BF25" s="58" t="s">
         <v>340</v>
       </c>
-      <c r="BG25" s="66" t="s">
+      <c r="BG25" s="62" t="s">
         <v>346</v>
       </c>
-      <c r="BH25" s="66" t="s">
+      <c r="BH25" s="62" t="s">
         <v>353</v>
       </c>
     </row>
@@ -9034,7 +9034,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02F41974-3F33-4A2F-868D-4FBA97A033D8}">
   <dimension ref="B1:B7"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="75.85546875" bestFit="1" customWidth="1"/>
   </cols>
@@ -9082,7 +9082,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{356CA008-BCEA-4A99-A79F-FCC884D6E8C1}">
   <dimension ref="A1:G34"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -9541,7 +9541,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1633F340-5B77-4BB3-B5D5-C1FFFC050A5C}">
   <dimension ref="A1:R42"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21.140625" customWidth="1"/>
@@ -9575,18 +9575,18 @@
       <c r="F1" s="45" t="s">
         <v>62</v>
       </c>
-      <c r="G1" s="56" t="s">
+      <c r="G1" s="65" t="s">
         <v>197</v>
       </c>
-      <c r="H1" s="56"/>
-      <c r="I1" s="57"/>
-      <c r="J1" s="58" t="s">
+      <c r="H1" s="65"/>
+      <c r="I1" s="66"/>
+      <c r="J1" s="67" t="s">
         <v>218</v>
       </c>
-      <c r="K1" s="58"/>
-      <c r="L1" s="58"/>
-      <c r="M1" s="58"/>
-      <c r="N1" s="58"/>
+      <c r="K1" s="67"/>
+      <c r="L1" s="67"/>
+      <c r="M1" s="67"/>
+      <c r="N1" s="67"/>
     </row>
     <row r="2" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
@@ -11214,10 +11214,10 @@
       <c r="R36" s="49"/>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="J38" s="59" t="s">
+      <c r="J38" s="68" t="s">
         <v>265</v>
       </c>
-      <c r="K38" s="59"/>
+      <c r="K38" s="68"/>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J39" s="43" t="s">
